--- a/base_ncm_imp.xlsx
+++ b/base_ncm_imp.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ghpcbr-my.sharepoint.com/personal/compras_ghpc_com_br/Documents/Área de Trabalho/Projeto Calc-Importação/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="145" documentId="8_{F3E0E2C0-1212-41DE-AB57-D81143ED4440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2F90B9D-4482-4C82-9A60-644B16928C68}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="8_{F3E0E2C0-1212-41DE-AB57-D81143ED4440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6031968E-70D6-46CE-A027-65B0E410074F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{F3A60253-5446-4A89-8639-9F9D3D2C0B62}"/>
   </bookViews>
@@ -105,17 +105,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -466,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7332B7F-3B84-4832-A819-D7FC5C2921D2}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1486,6 +1476,26 @@
         <v>9.6500000000000002E-2</v>
       </c>
       <c r="F51" s="1">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>76041029</v>
+      </c>
+      <c r="B52" s="1">
+        <v>0</v>
+      </c>
+      <c r="C52" s="1">
+        <v>0.108</v>
+      </c>
+      <c r="D52" s="1">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="E52" s="1">
+        <v>9.6500000000000002E-2</v>
+      </c>
+      <c r="F52" s="1">
         <v>0.18</v>
       </c>
     </row>
